--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -19,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,14 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -603,9 +603,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -677,9 +674,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -708,9 +702,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -782,9 +773,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -813,9 +801,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -887,9 +872,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -961,9 +943,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -992,9 +971,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -1023,9 +999,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1054,9 +1027,6 @@
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -1085,9 +1055,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -1116,9 +1083,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -1147,9 +1111,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -1178,9 +1139,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1167,6 @@
           <t>Manila, Filipina</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -1240,9 +1195,6 @@
           <t>Sumatera Selatan</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -1418,7 +1370,7 @@
           <t>K-0015</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="5" t="n">
         <v>45435.375</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -1483,10 +1435,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1500,7 +1448,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1508,7 +1455,7 @@
           <t>K-0004</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="5" t="n">
         <v>44032.375</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1573,14 +1520,11 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>K-0003</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1594,7 +1538,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1602,7 +1545,7 @@
           <t>K-0033</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>45635.375</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1667,10 +1610,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1684,7 +1623,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1692,7 +1630,7 @@
           <t>K-0044</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>44914.375</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -1757,10 +1695,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1774,7 +1708,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1782,7 +1715,7 @@
           <t>K-0006</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>45716.375</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1847,14 +1780,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>K-0003</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1868,7 +1798,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1876,7 +1805,7 @@
           <t>K-0031</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>45026.375</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1941,10 +1870,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -1958,7 +1883,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1966,7 +1890,7 @@
           <t>K-0009</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>45768.375</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -2031,10 +1955,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -2048,7 +1968,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2056,7 +1975,7 @@
           <t>K-0043</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>44308.375</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -2121,10 +2040,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -2138,7 +2053,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2146,7 +2060,7 @@
           <t>K-0045</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>45424.375</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -2211,14 +2125,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>K-0046</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>Habis</t>
@@ -2232,7 +2143,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2240,7 +2150,7 @@
           <t>K-0039</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>44395.375</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -2305,10 +2215,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2322,7 +2228,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2330,7 +2235,7 @@
           <t>K-0042</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>45859.375</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -2395,14 +2300,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>K-0041</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2416,7 +2318,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2424,7 +2325,7 @@
           <t>K-0036</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>45132.375</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -2489,10 +2390,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2506,7 +2403,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2514,7 +2410,7 @@
           <t>K-0046</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>45870.375</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -2579,10 +2475,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2596,7 +2488,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2604,7 +2495,7 @@
           <t>K-0041</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>45158.375</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -2669,10 +2560,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2686,7 +2573,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2694,7 +2580,7 @@
           <t>K-0047</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>45527.375</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -2759,14 +2645,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>K-0048</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2780,7 +2663,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2788,7 +2670,7 @@
           <t>K-0010</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>45165.375</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -2853,14 +2735,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>K-0007</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2874,7 +2753,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2882,7 +2760,7 @@
           <t>K-0012</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>45901.375</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -2947,10 +2825,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -2964,7 +2838,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2972,7 +2845,7 @@
           <t>K-0029</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>45923.375</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -3037,10 +2910,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
@@ -3054,7 +2923,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3062,7 +2930,7 @@
           <t>K-0037</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>45723.375</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -3127,14 +2995,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>K-0038</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3148,7 +3013,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3156,7 +3020,7 @@
           <t>K-0002</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>44665.375</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -3221,14 +3085,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>K-0003</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3242,7 +3103,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3250,7 +3110,7 @@
           <t>K-0024</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>45454.375</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -3315,10 +3175,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3332,7 +3188,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3340,7 +3195,7 @@
           <t>K-0032</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>45458.375</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -3405,10 +3260,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3422,7 +3273,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3430,7 +3280,7 @@
           <t>K-0011</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>45847.375</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -3495,10 +3345,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3512,7 +3358,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3520,7 +3365,7 @@
           <t>K-0025</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>45691.375</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -3585,10 +3430,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3602,7 +3443,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3610,7 +3450,7 @@
           <t>K-0027</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="5" t="n">
         <v>46064.375</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -3675,14 +3515,11 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>K-0028</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3696,7 +3533,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3704,7 +3540,7 @@
           <t>K-0014</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="5" t="n">
         <v>46108.375</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -3769,14 +3605,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>K-0015</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3790,7 +3623,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3798,7 +3630,7 @@
           <t>K-0038</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="5" t="n">
         <v>45058.375</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -3863,10 +3695,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3880,7 +3708,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3888,7 +3715,7 @@
           <t>K-0035</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="5" t="n">
         <v>46524.375</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -3953,10 +3780,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -3970,7 +3793,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3978,7 +3800,7 @@
           <t>K-0005</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="5" t="n">
         <v>45805.375</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -4043,10 +3865,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4060,7 +3878,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4068,7 +3885,7 @@
           <t>K-0023</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="5" t="n">
         <v>46553.375</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -4133,10 +3950,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4150,7 +3963,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4158,7 +3970,7 @@
           <t>K-0019</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="5" t="n">
         <v>46659.375</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -4223,14 +4035,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>K-0020</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4244,7 +4053,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4252,7 +4060,7 @@
           <t>K-0022</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="5" t="n">
         <v>45216.375</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -4317,10 +4125,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4334,7 +4138,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4342,7 +4145,7 @@
           <t>K-0021</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="5" t="n">
         <v>45978.375</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -4407,10 +4210,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4424,7 +4223,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4432,7 +4230,7 @@
           <t>K-0040</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="5" t="n">
         <v>46364.375</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -4497,10 +4295,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4514,7 +4308,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4522,7 +4315,7 @@
           <t>K-0003</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="5" t="n">
         <v>46000.375</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -4587,10 +4380,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4604,7 +4393,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4612,7 +4400,7 @@
           <t>K-0017</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="5" t="n">
         <v>45286.375</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -4677,10 +4465,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4694,7 +4478,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4702,7 +4485,7 @@
           <t>K-0008</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
+      <c r="B38" s="5" t="n">
         <v>46070.375</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -4767,14 +4550,11 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>K-0007</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4788,7 +4568,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4796,7 +4575,7 @@
           <t>K-0016</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="5" t="n">
         <v>46119.375</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -4861,10 +4640,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4878,7 +4653,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4886,7 +4660,7 @@
           <t>K-0026</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
+      <c r="B40" s="5" t="n">
         <v>46549.375</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -4951,10 +4725,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -4968,7 +4738,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4976,7 +4745,7 @@
           <t>K-0007</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="5" t="n">
         <v>45462.375</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -5041,10 +4810,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5058,7 +4823,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5066,7 +4830,7 @@
           <t>K-0001</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="5" t="n">
         <v>46924.375</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -5131,14 +4895,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>K-0003</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5152,7 +4913,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5160,7 +4920,7 @@
           <t>K-0020</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B43" s="5" t="n">
         <v>46221.375</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -5225,10 +4985,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5242,7 +4998,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5250,7 +5005,7 @@
           <t>K-0028</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="5" t="n">
         <v>46229.375</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -5315,10 +5070,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5332,7 +5083,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5340,7 +5090,7 @@
           <t>K-0048</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B45" s="5" t="n">
         <v>47048.375</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -5405,10 +5155,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5422,7 +5168,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5430,7 +5175,7 @@
           <t>K-0030</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B46" s="5" t="n">
         <v>46323.375</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -5495,14 +5240,11 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>K-0029</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5516,7 +5258,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5524,7 +5265,7 @@
           <t>K-0034</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="5" t="n">
         <v>45606.375</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -5589,10 +5330,6 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5606,7 +5343,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5614,7 +5350,7 @@
           <t>K-0013</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n">
+      <c r="B48" s="5" t="n">
         <v>47088.375</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -5679,14 +5415,11 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>K-0015</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5700,7 +5433,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5708,7 +5440,7 @@
           <t>K-0018</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B49" s="5" t="n">
         <v>46387.375</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -5773,10 +5505,6 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -5790,7 +5518,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +6263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://monitoring-kerjasama.vercel.app</t>
+          <t>https://simkerma.vercel.app</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6602,7 +6329,6 @@
           <t>WA_TARGET</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Nomor WhatsApp tujuan (mis. 62812xxxx), pisahkan koma</t>

--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://simkerma.vercel.app</t>
+          <t>https://sipakat-polkesbang.vercel.app</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://sipakat-polkesbang.vercel.app</t>
+          <t>https://simkerma.vercel.app</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -45,7 +46,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D9488"/>
+        <fgColor rgb="006D28D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -435,13 +436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -514,7 +515,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,10 +534,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="3">
@@ -557,12 +558,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ns. Rina</t>
+          <t>Ns. Rina Sari</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -576,10 +577,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="4">
@@ -590,7 +591,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RS Pelabuhan Palembang</t>
+          <t>RSUP dr. Mohammad Hoesin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -600,14 +601,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>dr. Bagus</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>humas@rsmh.co.id</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0711354088</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="5">
@@ -618,39 +634,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Puskesmas Sekip</t>
+          <t>RSUD Lahat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>dr. Maya</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>maya.sekip@dinkes.go.id</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>081255667788</t>
+          <t>Kab. Lahat, Sumsel</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="6">
@@ -661,7 +662,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puskesmas Kenten</t>
+          <t>Puskesmas Sekip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -671,14 +672,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dr. Maya</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>maya.sekip@dinkes.go.id</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>081255667788</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="7">
@@ -689,7 +705,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Puskesmas Plaju</t>
+          <t>Puskesmas Kenten</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -699,14 +715,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="8">
@@ -717,39 +733,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apotek Kimia Farma 41</t>
+          <t>Puskesmas Muara Enim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apotek</t>
+          <t>Puskesmas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Apt. Dewi</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>dewi@kimiafarma.co.id</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>081399887766</t>
+          <t>Kab. Muara Enim, Sumsel</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="9">
@@ -760,7 +761,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apotek Sehat Bersama</t>
+          <t>Apotek Kimia Farma 41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,14 +771,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Apt. Dewi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dewi@kimiafarma.co.id</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>081399887766</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="10">
@@ -798,14 +814,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="11">
@@ -826,7 +842,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -845,10 +861,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="12">
@@ -869,14 +885,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Banyuasin, Sumsel</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="13">
@@ -887,39 +903,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kota Palembang</t>
+          <t>PBM Bidan Yulianti</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kabupaten/Kota</t>
+          <t>Praktik Bidan Mandiri</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Kabid Yankes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>yankes@dinkespalembang.go.id</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0711350123</t>
+          <t>Kab. OKI, Sumsel</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="14">
@@ -930,24 +931,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IBI Cabang Palembang</t>
+          <t>Dinas Kesehatan Kota Palembang</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Organisasi Profesi</t>
+          <t>Dinas Kesehatan Kabupaten/Kota</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kabid Yankes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yankes@dinkespalembang.go.id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0711350123</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="15">
@@ -958,24 +974,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Magenta Language Academy</t>
+          <t>Dinas Kesehatan Provinsi Sumsel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Perusahaan</t>
+          <t>Dinas Kesehatan Provinsi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="16">
@@ -986,7 +1002,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Institut Teknologi Bandung</t>
+          <t>Universitas Sriwijaya</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -996,14 +1012,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>Kab. Ogan Ilir, Sumsel</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kabag Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>kerjasama@unsri.ac.id</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0711580069</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="17">
@@ -1024,14 +1055,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Kota Bekasi, Jabar</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="18">
@@ -1052,14 +1083,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="19">
@@ -1070,24 +1101,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Klinik Kadir Medika</t>
+          <t>IBI Cabang Palembang</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Klinik</t>
+          <t>Organisasi Profesi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="20">
@@ -1098,24 +1129,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Puskesmas Multiwahana</t>
+          <t>DPW PATELKI Sumsel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Organisasi Profesi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="21">
@@ -1126,24 +1157,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RSUD Lahat</t>
+          <t>Arellano University</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Luar Negeri</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Manila, Filipina</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prof. Santos</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>partnership@arellano.edu.ph</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+63285551234</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="22">
@@ -1154,7 +1200,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arellano University</t>
+          <t>Hiroshima University</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1164,14 +1210,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Manila, Filipina</t>
+          <t>Hiroshima, Jepang</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46198</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="23">
@@ -1182,24 +1228,304 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dinas Perpustakaan Provinsi Sumsel</t>
+          <t>PT Enseval Putera Megatrading Tbk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Perusahaan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PT Kimia Farma Tbk</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Perusahaan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Perpustakaan Nasional RI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Perpustakaan</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sumatera Selatan</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>46198</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M-0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dinas Perpustakaan Prov. Sumsel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Perpustakaan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Prov. Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BNN Provinsi Sumsel</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Prov. Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Balai Besar POM Palembang</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Badan POM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi/Kabupaten/Kota</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau, Sumsel</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KKP Kelas II Palembang</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UPT Vertikal Kemenkes</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>M-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Poskesdes Lubuk Ampelas</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Poskesdes</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kab. Muara Enim, Sumsel</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LAM-PTKes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LAMPTKes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>M-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SLB Negeri Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau, Sumsel</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>46216</v>
       </c>
     </row>
   </sheetData>
@@ -1213,19 +1539,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -1235,7 +1561,7 @@
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
     <col width="17" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
@@ -1367,81 +1693,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K-0015</t>
+          <t>K-0012</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>45435.375</v>
+        <v>45506.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Puskesmas Sekip</t>
+          <t>Hiroshima University</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Luar Negeri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Hiroshima, Jepang</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/285</t>
+          <t>HK.03.01/1.3/388</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Memorandum of Agreement (MoA)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni</t>
+          <t>Penelitian, Penerapan Teknologi</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Prodi Profesi Bidan</t>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>President/Dean</t>
         </is>
       </c>
       <c r="L2" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>45435</v>
+        <v>45506</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>45799</v>
+        <v>46235</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Riset bersama; konfirmasi lanjut</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Habis</t>
+          <t>Segera Berakhir</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>-399</v>
+        <v>19</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1452,20 +1783,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K-0004</t>
+          <t>K-0023</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44032.375</v>
+        <v>45516.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>M-0004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RSUD Palembang BARI</t>
+          <t>RSUD Lahat</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1475,12 +1806,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Lahat, Sumsel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/296</t>
+          <t>HK.03.01/1.3/377</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1490,12 +1821,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni, Penelitian, Penerapan Teknologi</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Prodi DIII Keperawatan Kampus Baturaja</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1504,34 +1835,29 @@
         </is>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>44032</v>
+        <v>45516</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>45857</v>
+        <v>46245</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>K-0003</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Habis</t>
+          <t>Segera Berakhir</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>-341</v>
+        <v>29</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1542,81 +1868,91 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K-0033</t>
+          <t>K-0003</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>45635.375</v>
+        <v>45531.375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M-0012</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kota Palembang</t>
+          <t>RSUD Palembang BARI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kabupaten/Kota</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/267</t>
+          <t>HK.03.01/1.3/397</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+          <t>Prodi DIII Kebidanan Palembang</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kepala Dinas</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>45635</v>
+        <v>45531</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>45999</v>
+        <v>46260</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Segera jatuh tempo, siapkan perpanjangan</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Habis</t>
+          <t>Segera Berakhir</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>-199</v>
+        <v>44</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1627,68 +1963,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K-0044</t>
+          <t>K-0017</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>44914.375</v>
+        <v>45911.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M-0017</t>
+          <t>M-0010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BBLK Palembang</t>
+          <t>PBM Bidan Sri Wahyuni</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Balai Besar Laboratorium Kesehatan (BBLK)</t>
+          <t>Praktik Bidan Mandiri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/256</t>
+          <t>HK.03.01/1.3/383</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Penelitian</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+          <t>Prodi Sarjana Terapan Kebidanan</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kepala Balai</t>
+          <t>Bidan Pemilik</t>
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>44914</v>
+        <v>45911</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>46009</v>
+        <v>46275</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1697,11 +2033,11 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Habis</t>
+          <t>Segera Berakhir</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>-189</v>
+        <v>59</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1712,77 +2048,77 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K-0006</t>
+          <t>K-0005</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45716.375</v>
+        <v>45016.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RSUD Palembang BARI</t>
+          <t>Puskesmas Sekip</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Puskesmas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/294</t>
+          <t>HK.03.01/1.3/395</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Prodi Profesi Bidan</t>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Kepala Puskesmas</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3000000</v>
+        <v>500000</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>45716</v>
+        <v>45016</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46080</v>
+        <v>45746</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>K-0003</t>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Sudah diperpanjang</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1791,7 +2127,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>-118</v>
+        <v>-470</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1802,81 +2138,86 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K-0031</t>
+          <t>K-0018</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>45026.375</v>
+        <v>45811.375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M-0012</t>
+          <t>M-0011</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kota Palembang</t>
+          <t>PBM Bidan Marlina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kabupaten/Kota</t>
+          <t>Praktik Bidan Mandiri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Banyuasin, Sumsel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/269</t>
+          <t>HK.03.01/1.3/382</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Pendidikan</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kepala Dinas</t>
+          <t>Bidan Pemilik</t>
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5000000</v>
+        <v>300000</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>45026</v>
+        <v>45811</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46121</v>
+        <v>46175</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Habis baru-baru ini</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>-77</v>
+        <v>-41</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1887,20 +2228,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K-0009</t>
+          <t>K-0004</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45768.375</v>
+        <v>45456.375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RS Muhammadiyah Palembang</t>
+          <t>RSUD Palembang BARI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1910,22 +2251,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/291</t>
+          <t>HK.03.01/1.3/396</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Penelitian, Rekrutmen Alumni, Tridarma Perguruan Tinggi</t>
+          <t>Pendidikan, Penerapan Teknologi</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1939,29 +2280,39 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>45768</v>
+        <v>45456</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46132</v>
+        <v>46185</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra untuk perpanjangan</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>-66</v>
+        <v>-31</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1972,72 +2323,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K-0043</t>
+          <t>K-0016</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>44308.375</v>
+        <v>45851.375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M-0017</t>
+          <t>M-0006</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BBLK Palembang</t>
+          <t>Puskesmas Kenten</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Balai Besar Laboratorium Kesehatan (BBLK)</t>
+          <t>Puskesmas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/257</t>
+          <t>HK.03.01/1.3/384</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Addendum</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Beasiswa</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Prodi Profesi Bidan</t>
+          <t>Prodi DIII Kebidanan Palembang</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kepala Balai</t>
+          <t>Kepala Puskesmas</t>
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>44308</v>
+        <v>45851</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>46133</v>
+        <v>46215</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Berakhir hari ini — segera tindak lanjut</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2046,7 +2402,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>-65</v>
+        <v>-1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2057,86 +2413,86 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K-0045</t>
+          <t>K-0013</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45424.375</v>
+        <v>46016.375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M-0018</t>
+          <t>M-0022</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Klinik Kadir Medika</t>
+          <t>PT Enseval Putera Megatrading Tbk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Klinik</t>
+          <t>Perusahaan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/255</t>
+          <t>HK.03.01/1.3/387</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Surat Perjanjian Kerja Sama (Kontrak)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni, Penerapan Teknologi</t>
+          <t>Rekrutmen Alumni</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Direktorat Poltekkes Kemenkes Palembang</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Penanggung Jawab Klinik</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2000000</v>
+        <v>15000000</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>45424</v>
+        <v>46016</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46153</v>
+        <v>46380</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>K-0046</t>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kontrak penyediaan tenaga; nilai besar</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Habis</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>-45</v>
+        <v>164</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2147,35 +2503,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K-0039</t>
+          <t>K-0040</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>44395.375</v>
+        <v>46016.375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M-0015</t>
+          <t>M-0030</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Institut Teknologi Bandung</t>
+          <t>Poskesdes Lubuk Ampelas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Institusi Pendidikan (Non Poltekkes)</t>
+          <t>Poskesdes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>Kab. Muara Enim, Sumsel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/261</t>
+          <t>HK.03.01/1.3/360</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2185,43 +2541,43 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Penerapan Teknologi, Beasiswa</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Prodi DIII Farmasi</t>
+          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rektor</t>
+          <t>Bidan Desa</t>
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>44395</v>
+        <v>46016</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46220</v>
+        <v>46380</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2232,86 +2588,86 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K-0042</t>
+          <t>K-0015</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45859.375</v>
+        <v>45716.375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M-0016</t>
+          <t>M-0009</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Poltekkes Kemenkes Jakarta III</t>
+          <t>Klinik Sinar Abadi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Institusi Pendidikan (Poltekkes)</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/258</t>
+          <t>HK.03.01/1.3/385</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Beasiswa, Rekrutmen Alumni</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Direktur</t>
+          <t>Penanggung Jawab Klinik</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>45859</v>
+        <v>45716</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46223</v>
+        <v>46445</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>K-0041</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Tidak diperpanjang — klinik pindah kepemilikan</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2322,11 +2678,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K-0036</t>
+          <t>K-0009</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>45132.375</v>
+        <v>46196.375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2335,68 +2691,78 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IBI Cabang Palembang</t>
+          <t>Dinas Kesehatan Kota Palembang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Organisasi Profesi</t>
+          <t>Dinas Kesehatan Kabupaten/Kota</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/264</t>
+          <t>HK.03.01/1.3/391</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Addendum</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Prodi DIII Gizi</t>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ketua</t>
+          <t>Kepala Dinas</t>
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>45132</v>
+        <v>46196</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46227</v>
+        <v>46560</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>K-0007</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Addendum penambahan ruang lingkup</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2407,68 +2773,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K-0046</t>
+          <t>K-0026</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>45870.375</v>
+        <v>46201.375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M-0018</t>
+          <t>M-0008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Klinik Kadir Medika</t>
+          <t>Apotek Kimia Farma 41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Klinik</t>
+          <t>Apotek</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/254</t>
+          <t>HK.03.01/1.3/374</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Addendum</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Pendidikan, Rekrutmen Alumni</t>
+          <t>Rekrutmen Alumni</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Prodi DIII Teknologi Laboratorium Medis</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Penanggung Jawab Klinik</t>
+          <t>Apoteker Pengelola Apotek</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>45870</v>
+        <v>46201</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>46234</v>
+        <v>46565</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2477,11 +2843,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2492,68 +2858,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K-0041</t>
+          <t>K-0033</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>45158.375</v>
+        <v>45916.375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M-0016</t>
+          <t>M-0019</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Poltekkes Kemenkes Jakarta III</t>
+          <t>DPW PATELKI Sumsel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Institusi Pendidikan (Poltekkes)</t>
+          <t>Organisasi Profesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DKI Jakarta</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/259</t>
+          <t>HK.03.01/1.3/367</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Memorandum of Agreement (MoA)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Beasiswa</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Prodi DIII Farmasi</t>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Direktur</t>
+          <t>Ketua</t>
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>45158</v>
+        <v>45916</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46253</v>
+        <v>46645</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2562,11 +2928,11 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>55</v>
+        <v>429</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2577,35 +2943,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K-0047</t>
+          <t>K-0019</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45527.375</v>
+        <v>46116.375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M-0019</t>
+          <t>M-0012</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Puskesmas Multiwahana</t>
+          <t>PBM Bidan Yulianti</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Praktik Bidan Mandiri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. OKI, Sumsel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/253</t>
+          <t>HK.03.01/1.3/381</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2615,7 +2981,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Penerapan Teknologi, Penelitian</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2625,38 +2991,33 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Bidan Pemilik</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>45527</v>
+        <v>46116</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46256</v>
+        <v>46846</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>K-0048</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>58</v>
+        <v>630</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2667,86 +3028,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K-0010</t>
+          <t>K-0044</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45165.375</v>
+        <v>46196.375</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>M-0023</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RS Muhammadiyah Palembang</t>
+          <t>PT Kimia Farma Tbk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Perusahaan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/290</t>
+          <t>HK.03.01/1.3/356</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Surat Perjanjian Kerja Sama (Kontrak)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Beasiswa, Pendidikan, Rekrutmen Alumni</t>
+          <t>Rekrutmen Alumni</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Prodi DIII Gizi</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1500000</v>
+        <v>8000000</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>45165</v>
+        <v>46196</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46260</v>
+        <v>46926</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>K-0007</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>62</v>
+        <v>710</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2757,35 +3113,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K-0012</t>
+          <t>K-0042</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45901.375</v>
+        <v>46256.375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>M-0032</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RS Pelabuhan Palembang</t>
+          <t>SLB Negeri Lubuklinggau</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Lubuklinggau, Sumsel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/288</t>
+          <t>HK.03.01/1.3/358</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2795,43 +3151,43 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Rekrutmen Alumni, Penerapan Teknologi</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prodi DIII Teknologi Laboratorium Medis</t>
+          <t>Prodi DIII Keperawatan Gigi</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Rektor</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>45901</v>
+        <v>46256</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46265</v>
+        <v>46986</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>67</v>
+        <v>770</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2842,68 +3198,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K-0029</t>
+          <t>K-0032</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>45923.375</v>
+        <v>46286.375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M-0011</t>
+          <t>M-0018</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PBM Bidan Marlina</t>
+          <t>IBI Cabang Palembang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Praktik Bidan Mandiri</t>
+          <t>Organisasi Profesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/271</t>
+          <t>HK.03.01/1.3/368</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Memorandum of Agreement (MoA)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendidikan, Penerapan Teknologi</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi Profesi Bidan</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Bidan Pemilik</t>
+          <t>Ketua</t>
         </is>
       </c>
       <c r="L19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>45923</v>
+        <v>46286</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46287</v>
+        <v>47016</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2912,11 +3268,11 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Segera Berakhir</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>89</v>
+        <v>800</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2927,35 +3283,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K-0037</t>
+          <t>K-0039</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45723.375</v>
+        <v>46301.375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M-0014</t>
+          <t>M-0029</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Magenta Language Academy</t>
+          <t>KKP Kelas II Palembang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Perusahaan</t>
+          <t>UPT Vertikal Kemenkes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/263</t>
+          <t>HK.03.01/1.3/361</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2965,48 +3321,43 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi, Pengabdian kepada Masyarakat, Pendidikan</t>
+          <t>Pendidikan, Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Direktur</t>
+          <t>Kepala Kantor</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>2</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>45723</v>
+        <v>46301</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46452</v>
+        <v>47031</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>K-0038</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>254</v>
+        <v>815</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3017,20 +3368,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K-0002</t>
+          <t>K-0043</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>44665.375</v>
+        <v>46716.375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>M-0003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RSUD Palembang BARI</t>
+          <t>RSUP dr. Mohammad Hoesin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3040,27 +3391,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/298</t>
+          <t>HK.03.01/1.3/357</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Addendum</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Penelitian, Pengabdian kepada Masyarakat, Pendidikan</t>
+          <t>Penelitian</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3072,31 +3423,26 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>44665</v>
+        <v>46716</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46490</v>
+        <v>47081</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>K-0003</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>292</v>
+        <v>865</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3107,11 +3453,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K-0024</t>
+          <t>K-0025</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45454.375</v>
+        <v>46366.375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3120,7 +3466,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apotek Sehat Bersama</t>
+          <t>Apotek Kimia Farma 41</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3130,12 +3476,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/276</t>
+          <t>HK.03.01/1.3/375</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3145,12 +3491,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Penerapan Teknologi, Pendidikan, Rekrutmen Alumni</t>
+          <t>Pendidikan, Rekrutmen Alumni</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3162,13 +3508,13 @@
         <v>500000</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>45454</v>
+        <v>46366</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>46548</v>
+        <v>47096</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -3181,7 +3527,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3192,35 +3538,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K-0032</t>
+          <t>K-0002</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>45458.375</v>
+        <v>46016.375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M-0012</t>
+          <t>M-0001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kota Palembang</t>
+          <t>RSUD Palembang BARI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kabupaten/Kota</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/268</t>
+          <t>HK.03.01/1.3/398</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3230,43 +3576,48 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Penelitian, Penerapan Teknologi, Pengabdian kepada Masyarakat</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Prodi DIII Farmasi</t>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Kepala Dinas</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>45458</v>
+        <v>46016</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>46552</v>
+        <v>47111</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>K-0001</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>354</v>
+        <v>895</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3277,45 +3628,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K-0011</t>
+          <t>K-0006</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45847.375</v>
+        <v>46066.375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M-0003</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RS Pelabuhan Palembang</t>
+          <t>Puskesmas Sekip</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Puskesmas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/289</t>
+          <t>HK.03.01/1.3/394</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Penelitian, Tridarma Perguruan Tinggi</t>
+          <t>Pendidikan, Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3325,24 +3676,29 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Kepala Puskesmas</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1500000</v>
+        <v>750000</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>45847</v>
+        <v>46066</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>46576</v>
+        <v>47161</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Baru</t>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/395</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3351,7 +3707,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>378</v>
+        <v>945</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3362,45 +3718,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K-0025</t>
+          <t>K-0027</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>45691.375</v>
+        <v>45716.375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M-0009</t>
+          <t>M-0014</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Klinik Sinar Abadi</t>
+          <t>Dinas Kesehatan Provinsi Sumsel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Klinik</t>
+          <t>Dinas Kesehatan Provinsi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/275</t>
+          <t>HK.03.01/1.3/373</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Addendum</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Penelitian</t>
+          <t>Tridarma Perguruan Tinggi</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3410,20 +3766,20 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Penanggung Jawab Klinik</t>
+          <t>Kepala Dinas</t>
         </is>
       </c>
       <c r="L25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>45691</v>
+        <v>45716</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>46785</v>
+        <v>47176</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3436,7 +3792,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>587</v>
+        <v>960</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3447,77 +3803,77 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K-0027</t>
+          <t>K-0011</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>46064.375</v>
+        <v>46096.375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M-0010</t>
+          <t>M-0020</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PBM Bidan Sri Wahyuni</t>
+          <t>Arellano University</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Praktik Bidan Mandiri</t>
+          <t>Luar Negeri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Manila, Filipina</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/273</t>
+          <t>HK.03.01/1.3/389</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Memorandum of Agreement (MoA)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni, Penerapan Teknologi, Pendidikan</t>
+          <t>Pendidikan, Penelitian</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Prodi Profesi Bidan</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Bidan Pemilik</t>
+          <t>President/Dean</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>46064</v>
+        <v>46096</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>46793</v>
+        <v>47191</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>K-0028</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3526,7 +3882,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>595</v>
+        <v>975</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3537,68 +3893,68 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>K-0014</t>
+          <t>K-0008</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>46108.375</v>
+        <v>46116.375</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0013</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Puskesmas Sekip</t>
+          <t>Dinas Kesehatan Kota Palembang</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Dinas Kesehatan Kabupaten/Kota</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/286</t>
+          <t>HK.03.01/1.3/392</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Perjanjian Kerja sama (PKS) Operasional</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Penerapan Teknologi</t>
+          <t>Pengabdian kepada Masyarakat, Penyebaran Informasi</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Palembang</t>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Kepala Dinas</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>46108</v>
+        <v>46116</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>46838</v>
+        <v>47211</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3607,7 +3963,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>K-0015</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3616,7 +3972,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>640</v>
+        <v>995</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3627,72 +3983,72 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K-0038</t>
+          <t>K-0021</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>45058.375</v>
+        <v>46136.375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M-0014</t>
+          <t>M-0002</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Magenta Language Academy</t>
+          <t>RS Muhammadiyah Palembang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Perusahaan</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/262</t>
+          <t>HK.03.01/1.3/379</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi, Penerapan Teknologi, Beasiswa</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+          <t>Prodi DIII Keperawatan Gigi</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Direktur</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>45058</v>
+        <v>46136</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>46884</v>
+        <v>47231</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3701,7 +4057,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>686</v>
+        <v>1015</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3716,31 +4072,31 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>46524.375</v>
+        <v>46156.375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M-0013</t>
+          <t>M-0025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IBI Cabang Palembang</t>
+          <t>Dinas Perpustakaan Prov. Sumsel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Organisasi Profesi</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/265</t>
+          <t>HK.03.01/1.3/365</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3750,30 +4106,30 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni</t>
+          <t>Penyebaran Informasi</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+          <t>Direktorat Poltekkes Kemenkes Palembang</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ketua</t>
+          <t>Kepala</t>
         </is>
       </c>
       <c r="L29" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>46524</v>
+        <v>46156</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>46889</v>
+        <v>47251</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3786,7 +4142,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>691</v>
+        <v>1035</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3797,35 +4153,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>K-0005</t>
+          <t>K-0036</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>45805.375</v>
+        <v>46221.375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>M-0026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RSUD Palembang BARI</t>
+          <t>BNN Provinsi Sumsel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Badan Narkotika Nasional (BNN)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/295</t>
+          <t>HK.03.01/1.3/364</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3835,30 +4191,30 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Pendidikan, Penelitian</t>
+          <t>Pengabdian kepada Masyarakat, Penyebaran Informasi</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Kepala BNNP</t>
         </is>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>45805</v>
+        <v>46221</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>46900</v>
+        <v>47316</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3871,7 +4227,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>702</v>
+        <v>1100</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3882,68 +4238,68 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K-0023</t>
+          <t>K-0030</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>46553.375</v>
+        <v>46246.375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M-0008</t>
+          <t>M-0016</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apotek Sehat Bersama</t>
+          <t>Poltekkes Kemenkes Jakarta III</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Apotek</t>
+          <t>Institusi Pendidikan (Poltekkes)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Bekasi, Jabar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/277</t>
+          <t>HK.03.01/1.3/370</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Addendum</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Beasiswa</t>
+          <t>Pendidikan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Palembang</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Apoteker Pengelola Apotek</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>46553</v>
+        <v>46246</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>46918</v>
+        <v>47341</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3956,7 +4312,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>720</v>
+        <v>1125</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3967,86 +4323,81 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>K-0019</t>
+          <t>K-0007</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>46659.375</v>
+        <v>45616.375</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>M-0013</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Puskesmas Plaju</t>
+          <t>Dinas Kesehatan Kota Palembang</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Dinas Kesehatan Kabupaten/Kota</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/281</t>
+          <t>HK.03.01/1.3/393</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Penelitian, Pengabdian kepada Masyarakat, Tridarma Perguruan Tinggi</t>
+          <t>Tridarma Perguruan Tinggi</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Direktorat Poltekkes Kemenkes Palembang</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Kepala Dinas</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>46659</v>
+        <v>45616</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>47024</v>
+        <v>47441</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>K-0020</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>826</v>
+        <v>1225</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4057,35 +4408,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>K-0022</t>
+          <t>K-0037</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>45216.375</v>
+        <v>46436.375</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M-0007</t>
+          <t>M-0027</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apotek Kimia Farma 41</t>
+          <t>Balai Besar POM Palembang</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Apotek</t>
+          <t>Badan POM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/278</t>
+          <t>HK.03.01/1.3/363</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4095,34 +4446,34 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Penelitian</t>
+          <t>Penerapan Teknologi</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Apoteker Pengelola Apotek</t>
+          <t>Kepala Balai</t>
         </is>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>45216</v>
+        <v>46436</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>47042</v>
+        <v>47531</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4131,7 +4482,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>844</v>
+        <v>1315</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4142,72 +4493,72 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>K-0021</t>
+          <t>K-0031</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>45978.375</v>
+        <v>46466.375</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M-0007</t>
+          <t>M-0017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apotek Kimia Farma 41</t>
+          <t>BBLK Palembang</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Apotek</t>
+          <t>Balai Besar Laboratorium Kesehatan (BBLK)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/279</t>
+          <t>HK.03.01/1.3/369</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Addendum</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi, Rekrutmen Alumni</t>
+          <t>Pendidikan, Penerapan Teknologi</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Apoteker Pengelola Apotek</t>
+          <t>Kepala Balai</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>45978</v>
+        <v>46466</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>47073</v>
+        <v>47561</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4216,7 +4567,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>875</v>
+        <v>1345</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4227,35 +4578,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>K-0040</t>
+          <t>K-0024</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>46364.375</v>
+        <v>46516.375</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M-0015</t>
+          <t>M-0007</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Institut Teknologi Bandung</t>
+          <t>Puskesmas Muara Enim</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Institusi Pendidikan (Non Poltekkes)</t>
+          <t>Puskesmas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jawa Barat</t>
+          <t>Kab. Muara Enim, Sumsel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/260</t>
+          <t>HK.03.01/1.3/376</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4265,30 +4616,30 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Penelitian, Rekrutmen Alumni</t>
+          <t>Pendidikan, Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Rektor</t>
+          <t>Kepala Puskesmas</t>
         </is>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>46364</v>
+        <v>46516</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>47094</v>
+        <v>47611</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4301,7 +4652,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>896</v>
+        <v>1395</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4312,11 +4663,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>K-0003</t>
+          <t>K-0001</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>46000.375</v>
+        <v>45816.375</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4335,12 +4686,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/297</t>
+          <t>HK.03.01/1.3/399</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4350,12 +4701,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Penelitian</t>
+          <t>Pendidikan, Penelitian, Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Prodi DIII Gizi</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4364,16 +4715,16 @@
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>46000</v>
+        <v>45816</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>47095</v>
+        <v>47641</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4386,7 +4737,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>897</v>
+        <v>1425</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4397,45 +4748,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>K-0017</t>
+          <t>K-0028</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>45286.375</v>
+        <v>45866.375</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>M-0015</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Puskesmas Kenten</t>
+          <t>Universitas Sriwijaya</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Ogan Ilir, Sumsel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/283</t>
+          <t>HK.03.01/1.3/372</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Addendum</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi, Pendidikan, Penelitian</t>
+          <t>Pendidikan, Penelitian</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4445,7 +4796,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Rektor</t>
         </is>
       </c>
       <c r="L37" s="4" t="n">
@@ -4455,10 +4806,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>45286</v>
+        <v>45866</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>47112</v>
+        <v>47691</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4471,7 +4822,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>914</v>
+        <v>1475</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4482,40 +4833,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>K-0008</t>
+          <t>K-0029</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>46070.375</v>
+        <v>46616.375</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>M-0015</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RS Muhammadiyah Palembang</t>
+          <t>Universitas Sriwijaya</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Ogan Ilir, Sumsel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/292</t>
+          <t>HK.03.01/1.3/371</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4525,34 +4876,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+          <t>Prodi DIII Gizi</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Rektor</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>5000000</v>
+        <v>1500000</v>
       </c>
       <c r="M38" t="n">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>46070</v>
+        <v>46616</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>47165</v>
+        <v>47711</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>K-0007</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4561,7 +4907,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>967</v>
+        <v>1495</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4572,35 +4918,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K-0016</t>
+          <t>K-0010</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>46119.375</v>
+        <v>45916.375</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0020</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Puskesmas Sekip</t>
+          <t>Arellano University</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Luar Negeri</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Manila, Filipina</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/284</t>
+          <t>HK.03.01/1.3/390</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4610,30 +4956,30 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Beasiswa, Rekrutmen Alumni, Penelitian</t>
+          <t>Pendidikan, Penelitian</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>President/Dean</t>
         </is>
       </c>
       <c r="L39" s="4" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>46119</v>
+        <v>45916</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>47214</v>
+        <v>47741</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -4646,7 +4992,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>1016</v>
+        <v>1525</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4657,72 +5003,72 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>K-0026</t>
+          <t>K-0020</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>46549.375</v>
+        <v>45966.375</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>M-0009</t>
+          <t>M-0002</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Klinik Sinar Abadi</t>
+          <t>RS Muhammadiyah Palembang</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Klinik</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/274</t>
+          <t>HK.03.01/1.3/380</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Rekrutmen Alumni, Beasiswa</t>
+          <t>Pendidikan, Penelitian, Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Penanggung Jawab Klinik</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>46549</v>
+        <v>45966</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>47279</v>
+        <v>47791</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +5077,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>1081</v>
+        <v>1575</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4742,68 +5088,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>K-0007</t>
+          <t>K-0014</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>45462.375</v>
+        <v>46716.375</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>M-0002</t>
+          <t>M-0023</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RS Muhammadiyah Palembang</t>
+          <t>PT Kimia Farma Tbk</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Perusahaan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/293</t>
+          <t>HK.03.01/1.3/386</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Penelitian, Beasiswa</t>
+          <t>Pendidikan, Rekrutmen Alumni</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Prodi DIII Farmasi</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1500000</v>
+        <v>5000000</v>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>45462</v>
+        <v>46716</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>47287</v>
+        <v>47811</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -4816,7 +5162,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>1089</v>
+        <v>1595</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4827,86 +5173,81 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>K-0001</t>
+          <t>K-0038</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>46924.375</v>
+        <v>46126.375</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M-0001</t>
+          <t>M-0028</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RSUD Palembang BARI</t>
+          <t>Pemerintah Kota Lubuklinggau</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rumah Sakit</t>
+          <t>Pemerintah Provinsi/Kabupaten/Kota</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Lubuklinggau, Sumsel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/299</t>
+          <t>HK.03.01/1.3/362</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Pendidikan, Penerapan Teknologi</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Prodi Sarjana Terapan Kebidanan</t>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Direktur RS</t>
+          <t>Wali Kota</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>46924</v>
+        <v>46126</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>47288</v>
+        <v>47951</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>K-0003</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>1090</v>
+        <v>1735</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4917,72 +5258,72 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K-0020</t>
+          <t>K-0022</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>46221.375</v>
+        <v>46916.375</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M-0006</t>
+          <t>M-0003</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Puskesmas Plaju</t>
+          <t>RSUP dr. Mohammad Hoesin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/280</t>
+          <t>HK.03.01/1.3/378</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nota Kesepahaman Bersama (MoU)</t>
+          <t>Perjanjian Kerja sama (PKS)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Beasiswa, Tridarma Perguruan Tinggi</t>
+          <t>Pendidikan, Penelitian</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>46221</v>
+        <v>46916</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>47316</v>
+        <v>48010</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4991,7 +5332,7 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>1118</v>
+        <v>1794</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5002,35 +5343,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>K-0028</t>
+          <t>K-0041</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>46229.375</v>
+        <v>46816.375</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M-0010</t>
+          <t>M-0031</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PBM Bidan Sri Wahyuni</t>
+          <t>LAM-PTKes</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Praktik Bidan Mandiri</t>
+          <t>LAMPTKes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/272</t>
+          <t>HK.03.01/1.3/359</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5040,34 +5381,34 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Penerapan Teknologi</t>
+          <t>Tridarma Perguruan Tinggi</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Palembang</t>
+          <t>Direktorat Poltekkes Kemenkes Palembang</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Bidan Pemilik</t>
+          <t>Direktur Eksekutif</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>46229</v>
+        <v>46816</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>47324</v>
+        <v>48641</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
+          <t>Baru</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5076,7 +5417,7 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>1126</v>
+        <v>2425</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5087,35 +5428,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>K-0048</t>
+          <t>K-0034</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>47048.375</v>
+        <v>47116.375</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>M-0019</t>
+          <t>M-0024</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Puskesmas Multiwahana</t>
+          <t>Perpustakaan Nasional RI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Puskesmas</t>
+          <t>Perpustakaan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>DKI Jakarta</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/252</t>
+          <t>HK.03.01/1.3/366</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5125,30 +5466,30 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tridarma Perguruan Tinggi, Pendidikan</t>
+          <t>Penyebaran Informasi</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Prodi DIII Gizi</t>
+          <t>Direktorat Poltekkes Kemenkes Palembang</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Kepala Puskesmas</t>
+          <t>Kepala</t>
         </is>
       </c>
       <c r="L45" s="4" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>47048</v>
+        <v>47116</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>47412</v>
+        <v>48941</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5161,7 +5502,7 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>1214</v>
+        <v>2725</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5172,190 +5513,195 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>K-0030</t>
+          <t>K-0045</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>46323.375</v>
+        <v>46077.375</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>M-0011</t>
+          <t>M-0004</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PBM Bidan Marlina</t>
+          <t>RSUD Lahat</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Praktik Bidan Mandiri</t>
+          <t>Rumah Sakit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kab. Lahat, Sumsel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/270</t>
+          <t>HK.03.01/1.3/455</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Memorandum of Agreement (MoA)</t>
+          <t>Addendum</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Penelitian, Rekrutmen Alumni</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Prodi DIII Kesehatan Lingkungan</t>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Bidan Pemilik</t>
+          <t>Direktur RS</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
         <v>2000000</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>46323</v>
+        <v>46077</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>47418</v>
+        <v>46441</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Perpanjangan</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>K-0029</t>
-        </is>
-      </c>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>1220</v>
+        <v>225</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>K-0034</t>
+          <t>K-0046</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>45606.375</v>
+        <v>44692.375</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M-0012</t>
+          <t>M-0020</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kota Palembang</t>
+          <t>Arellano University</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan Kabupaten/Kota</t>
+          <t>Luar Negeri</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Manila, Filipina</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/266</t>
+          <t>HK.03.01/1.3/454</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Perjanjian Kerja sama (PKS) Operasional</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Beasiswa, Penerapan Teknologi, Pengabdian kepada Masyarakat</t>
+          <t>Pengabdian kepada Masyarakat</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Prodi DIII Gizi</t>
+          <t>Prodi DIII Kebidanan Palembang</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kepala Dinas</t>
+          <t>President/Dean</t>
         </is>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>45606</v>
+        <v>44692</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>47431</v>
+        <v>45787</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Habis</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>1233</v>
+        <v>-429</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>K-0013</t>
+          <t>K-0047</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>47088.375</v>
+        <v>45132.375</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M-0004</t>
+          <t>M-0005</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5370,27 +5716,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sumatera Selatan</t>
+          <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HK.03.01/1.3/287</t>
+          <t>HK.03.01/1.3/453</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Perjanjian Kerja sama (PKS)</t>
+          <t>Addendum</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Pengabdian kepada Masyarakat, Tridarma Perguruan Tinggi, Pendidikan</t>
+          <t>Pendidikan, Penelitian</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Prodi DIII Kebidanan Palembang</t>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5402,122 +5748,2621 @@
         <v>2000000</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>47088</v>
+        <v>45132</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>47452</v>
+        <v>46227</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>K-0015</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Segera Berakhir</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>1254</v>
+        <v>11</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>K-0018</t>
+          <t>K-0048</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>46387.375</v>
+        <v>46229.375</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M-0005</t>
+          <t>M-0030</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Poskesdes Lubuk Ampelas</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Poskesdes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kab. Muara Enim, Sumsel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/452</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Pengabdian kepada Masyarakat</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bidan Desa</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>46959</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>743</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>K-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>46535.375</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>M-0032</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SLB Negeri Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau, Sumsel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/451</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Memorandum of Agreement (MoA)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Palembang</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Rektor</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>46535</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>47265</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>1049</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>K-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>44894.375</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>M-0010</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PBM Bidan Sri Wahyuni</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Praktik Bidan Mandiri</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/450</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bidan Pemilik</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>44894</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>-227</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>K-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44701.375</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>M-0032</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SLB Negeri Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau, Sumsel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/449</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Palembang</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Rektor</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>44701</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>-420</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>K-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>44434.375</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>M-0004</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>RSUD Lahat</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Rumah Sakit</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kab. Lahat, Sumsel</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/448</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS) Operasional</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Tridarma Perguruan Tinggi</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Direktur RS</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M53" t="n">
+        <v>5</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>44434</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>43</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>K-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>45389.375</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>M-0030</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Poskesdes Lubuk Ampelas</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Poskesdes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kab. Muara Enim, Sumsel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/447</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bidan Desa</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>45389</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>-98</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>K-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>44426.375</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>M-0009</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Klinik Sinar Abadi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Klinik</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/446</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Penerapan Teknologi</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Penanggung Jawab Klinik</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>44426</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>35</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>K-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>44967.375</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>M-0026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BNN Provinsi Sumsel</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Prov. Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/445</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Penerapan Teknologi</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Kampus Muara Enim</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Kepala BNNP</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>44967</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>-154</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>K-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>45875.375</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>M-0025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Dinas Perpustakaan Prov. Sumsel</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Perpustakaan</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Prov. Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/444</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Pengabdian kepada Masyarakat</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Prodi Sarjana Terapan Kebidanan</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Kepala</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>23</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>K-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>45148.375</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>M-0032</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SLB Negeri Lubuklinggau</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kota Lubuklinggau, Sumsel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/443</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Memorandum of Agreement (MoA)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Pendidikan, Pengabdian kepada Masyarakat</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Rektor</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>45148</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>27</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>K-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>47037.375</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M-0021</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Hiroshima University</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Luar Negeri</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Hiroshima, Jepang</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/442</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>President/Dean</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>47037</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>47401</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Proses perpanjangan</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>1185</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>K-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>45917.375</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>M-0026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BNN Provinsi Sumsel</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Badan Narkotika Nasional (BNN)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Prov. Sumatera Selatan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/441</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS) Operasional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Penerapan Teknologi</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Kepala BNNP</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>65</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>K-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>45870.375</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M-0029</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>KKP Kelas II Palembang</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>UPT Vertikal Kemenkes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/440</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Memorandum of Agreement (MoA)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Palembang</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Kepala Kantor</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>18</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>K-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>45303.375</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>M-0024</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Perpustakaan Nasional RI</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Perpustakaan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/439</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Pendidikan, Penelitian</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Prodi Profesi Bidan</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Kepala</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>45303</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>46398</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>182</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>K-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>45996.375</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>M-0023</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PT Kimia Farma Tbk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Perusahaan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/438</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Palembang</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>47091</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>875</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>K-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>45432.375</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>M-0031</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LAM-PTKes</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LAMPTKes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/437</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Penelitian</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>45432</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>-55</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>K-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>45127.375</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>M-0011</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PBM Bidan Marlina</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Praktik Bidan Mandiri</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kab. Banyuasin, Sumsel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/436</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Beasiswa</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bidan Pemilik</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>45127</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>6</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>K-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>45054.375</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>M-0006</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>Puskesmas Kenten</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Puskesmas</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Sumatera Selatan</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>HK.03.01/1.3/282</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/435</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Rekrutmen Alumni</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Prodi Sarjana Terapan Kebidanan</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Kepala Puskesmas</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M66" t="n">
+        <v>5</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>45054</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>46880</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>664</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>K-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>45149.375</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>M-0015</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Universitas Sriwijaya</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Institusi Pendidikan (Non Poltekkes)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kab. Ogan Ilir, Sumsel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/434</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Penerapan Teknologi</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Rektor</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>45149</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>28</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>K-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44365.375</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>M-0023</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PT Kimia Farma Tbk</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Perusahaan</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/433</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Pendidikan, Pengabdian kepada Masyarakat</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>44365</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>-26</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>K-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>43873.375</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>M-0029</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>KKP Kelas II Palembang</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UPT Vertikal Kemenkes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/432</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Memorandum of Agreement (MoA)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Rekrutmen Alumni</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kebidanan Palembang</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Kepala Kantor</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M69" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>43873</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>45699</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>-517</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>K-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>45899.375</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>M-0031</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LAM-PTKes</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LAMPTKes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/431</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Tridarma Perguruan Tinggi</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Prodi Profesi Bidan</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>47</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>K-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>44318.375</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>M-0006</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Puskesmas Kenten</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Puskesmas</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/430</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>Nota Kesepahaman Bersama (MoU)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Penelitian, Pendidikan, Rekrutmen Alumni</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pendidikan, Penelitian</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>Prodi DIII Kesehatan Lingkungan</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Kepala Puskesmas</t>
         </is>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="L71" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>44318</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>-73</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>K-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>44177.375</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>M-0006</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Puskesmas Kenten</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Puskesmas</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/429</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Nota Kesepahaman Bersama (MoU)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Penerapan Teknologi</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Poltekkes Kementerian Kesehatan Palembang</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Kepala Puskesmas</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>44177</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>-214</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>K-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>45875.375</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>M-0009</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Klinik Sinar Abadi</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Klinik</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/428</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Addendum</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Tridarma Perguruan Tinggi</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Direktorat Poltekkes Kemenkes Palembang</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Penanggung Jawab Klinik</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Perpanjangan</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Perlu addendum</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>23</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>K-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>45195.375</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>M-0010</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PBM Bidan Sri Wahyuni</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Praktik Bidan Mandiri</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/427</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Prodi DIII Keperawatan Kampus Palembang</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bidan Pemilik</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>3</v>
       </c>
-      <c r="N49" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>47482</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Perpanjangan</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>1284</v>
-      </c>
-      <c r="W49" t="inlineStr">
+      <c r="N74" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Proses perpanjangan</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>74</v>
+      </c>
+      <c r="W74" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>K-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>45826.375</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>M-0013</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Dinas Kesehatan Kota Palembang</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Dinas Kesehatan Kabupaten/Kota</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/426</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Memorandum of Agreement (MoA)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Pendidikan, Penelitian</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Prodi DIII Teknologi Laboratorium Medis</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Kepala Dinas</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Menunggu konfirmasi mitra</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>K-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>45809.375</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>M-0027</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Balai Besar POM Palembang</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Badan POM</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kota Palembang, Sumsel</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>HK.03.01/1.3/425</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS) Operasional</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Rekrutmen Alumni</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Prodi DIII Kesehatan Lingkungan</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Kepala Balai</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>-43</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -12,19 +12,23 @@
     <sheet name="Dataset" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pengaturan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mitra'!$A$1:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kerjasama'!$A$1:$X$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dataset'!$A$1:$B$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pengaturan'!$A$1:$C$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +40,34 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF92400E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFB91C1C"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF166534"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1E1B4B"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -49,8 +79,28 @@
         <fgColor rgb="006D28D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F46E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -58,11 +108,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -71,6 +135,21 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,65 +512,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF4F46E5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID Mitra</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Nama Mitra</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Jenis Mitra</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Wilayah/Provinsi</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>PIC Nama</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>PIC Email</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>PIC HP</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Jumlah Kerjasama</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Terakhir Update</t>
         </is>
@@ -647,6 +727,21 @@
           <t>Kab. Lahat, Sumsel</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rsud.lahat@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>628120000003</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -718,6 +813,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>puskesmas.kenten@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>628120000005</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
@@ -746,6 +856,21 @@
           <t>Kab. Muara Enim, Sumsel</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>puskesmas.muara.enim@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>628120000006</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -817,6 +942,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>klinik.sinar.abadi@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>628120000008</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
@@ -888,6 +1028,21 @@
           <t>Kab. Banyuasin, Sumsel</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pbm.bidan.marlina@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>628120000010</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -916,6 +1071,21 @@
           <t>Kab. OKI, Sumsel</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pbm.bidan.yulianti@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>628120000011</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -987,6 +1157,21 @@
           <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dinas.kesehatan.provinsi.sumsel@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>628120000013</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -1058,6 +1243,21 @@
           <t>Kota Bekasi, Jabar</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>poltekkes.kemenkes.jakarta.iii@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>628120000015</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -1086,6 +1286,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>bblk.palembang@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>628120000016</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -1114,6 +1329,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ibi.cabang.palembang@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>628120000017</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
@@ -1142,6 +1372,21 @@
           <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>dpw.patelki.sumsel@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>628120000018</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -1213,6 +1458,21 @@
           <t>Hiroshima, Jepang</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>hiroshima.university@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>628120000020</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -1241,6 +1501,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pt.enseval.putera.megatrading.tbk@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>628120000021</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -1269,6 +1544,21 @@
           <t>DKI Jakarta</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pt.kimia.farma.tbk@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>628120000022</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -1297,6 +1587,21 @@
           <t>DKI Jakarta</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>perpustakaan.nasional.ri@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>628120000023</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -1325,6 +1630,21 @@
           <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>dinas.perpustakaan.prov.sumsel@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>628120000024</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -1353,6 +1673,21 @@
           <t>Prov. Sumatera Selatan</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>bnn.provinsi.sumsel@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>628120000025</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -1381,6 +1716,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>balai.besar.pom.palembang@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>628120000026</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -1409,6 +1759,21 @@
           <t>Kota Lubuklinggau, Sumsel</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pemerintah.kota.lubuklinggau@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>628120000027</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -1437,6 +1802,21 @@
           <t>Kota Palembang, Sumsel</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kkp.kelas.ii.palembang@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>628120000028</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -1465,6 +1845,21 @@
           <t>Kab. Muara Enim, Sumsel</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>poskesdes.lubuk.ampelas@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>628120000029</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -1493,6 +1888,21 @@
           <t>DKI Jakarta</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lam.ptkes@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>628120000030</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -1521,6 +1931,21 @@
           <t>Kota Lubuklinggau, Sumsel</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bagian Kerja Sama</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>slb.negeri.lubuklinggau@contoh.mitra.id</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>628120000031</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -1529,6 +1954,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1536,155 +1962,156 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1E1B4B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID Kerjasama</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>ID Mitra</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Nama Mitra</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Jenis Mitra</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Wilayah/Provinsi</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Nomor Surat</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Bentuk Kerja Sama</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Ruang Lingkup</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Pengguna MoU/PKS</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Jabatan Penandatangan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Biaya (Rp)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Masa Berlaku (tahun)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Tanggal Mulai</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Tanggal Berakhir</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Jenis Entri</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Ref Kerjasama Sebelumnya</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Dokumen Induk (MoU)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>Link File MoU/PKS</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>Sisa Hari</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Diinput Oleh</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Reminder Terakhir</t>
         </is>
@@ -1766,7 +2193,7 @@
           <t>Riset bersama; konfirmasi lanjut</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -1851,7 +2278,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -1946,7 +2373,7 @@
           <t>Segera jatuh tempo, siapkan perpanjangan</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -2031,7 +2458,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -2121,7 +2548,7 @@
           <t>Sudah diperpanjang</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -2211,7 +2638,7 @@
           <t>Habis baru-baru ini</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -2306,7 +2733,7 @@
           <t>Menunggu konfirmasi mitra untuk perpanjangan</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -2396,7 +2823,7 @@
           <t>Berakhir hari ini — segera tindak lanjut</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -2486,7 +2913,7 @@
           <t>Kontrak penyediaan tenaga; nilai besar</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -2571,7 +2998,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -2661,7 +3088,7 @@
           <t>Tidak diperpanjang — klinik pindah kepemilikan</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -2756,7 +3183,7 @@
           <t>Addendum penambahan ruang lingkup</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -2841,7 +3268,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -2926,7 +3353,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3011,7 +3438,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3096,7 +3523,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3181,7 +3608,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3266,7 +3693,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3351,7 +3778,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3436,7 +3863,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U21" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3521,7 +3948,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3611,7 +4038,7 @@
           <t>K-0001</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3701,7 +4128,7 @@
           <t>HK.03.01/1.3/395</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U24" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3786,7 +4213,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3876,7 +4303,7 @@
           <t>K-0010</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -3966,7 +4393,7 @@
           <t>K-0007</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U27" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4051,7 +4478,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U28" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4136,7 +4563,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U29" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4221,7 +4648,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U30" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4306,7 +4733,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U31" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4391,7 +4818,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U32" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4476,7 +4903,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U33" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4561,7 +4988,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U34" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4646,7 +5073,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U35" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4731,7 +5158,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U36" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4816,7 +5243,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U37" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4901,7 +5328,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U38" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -4986,7 +5413,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U39" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5071,7 +5498,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="U40" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5156,7 +5583,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U41" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5241,7 +5668,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U42" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5326,7 +5753,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U43" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5411,7 +5838,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U44" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5496,7 +5923,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U45" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5581,11 +6008,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
+      <c r="U46" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5598,7 +6021,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5671,11 +6093,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -5688,7 +6106,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5761,11 +6178,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
+      <c r="U48" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -5778,7 +6191,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5851,15 +6263,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="U49" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5872,7 +6281,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5945,15 +6353,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U50" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -5966,7 +6371,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6039,15 +6443,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -6060,7 +6461,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6133,11 +6533,7 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -6150,7 +6546,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6223,11 +6618,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
+      <c r="U53" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6240,7 +6631,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6313,15 +6703,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -6334,7 +6721,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6407,11 +6793,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
+      <c r="U55" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6424,7 +6806,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6497,15 +6878,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -6518,7 +6896,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6591,11 +6968,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
+      <c r="U57" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6608,7 +6981,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6681,15 +7053,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U58" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6702,7 +7071,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6775,15 +7143,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
           <t>Proses perpanjangan</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="U59" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -6796,7 +7161,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6869,11 +7233,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
+      <c r="U60" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6886,7 +7246,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6959,11 +7318,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
+      <c r="U61" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -6976,7 +7331,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7049,15 +7403,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="U62" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -7070,7 +7421,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7143,11 +7493,7 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
+      <c r="U63" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -7160,7 +7506,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7233,11 +7578,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -7250,7 +7591,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7323,15 +7663,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U65" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -7344,7 +7681,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7417,15 +7753,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="U66" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
@@ -7438,7 +7771,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7511,11 +7843,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
+      <c r="U67" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -7528,7 +7856,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7601,15 +7928,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="U68" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -7622,7 +7946,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7695,11 +8018,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr">
+      <c r="U69" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -7712,7 +8031,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7785,15 +8103,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="U70" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -7806,7 +8121,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7879,15 +8193,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="U71" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -7900,7 +8211,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7973,11 +8283,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr">
+      <c r="U72" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -7990,7 +8296,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8063,15 +8368,12 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="U73" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -8084,7 +8386,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8157,15 +8458,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
           <t>Proses perpanjangan</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="U74" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
@@ -8178,7 +8476,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8251,15 +8548,12 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="U75" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -8272,7 +8566,6 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8345,11 +8638,7 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr">
+      <c r="U76" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
@@ -8362,9 +8651,9 @@
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8372,23 +8661,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF475569"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Nilai</t>
         </is>
@@ -9031,6 +9321,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9038,166 +9329,278 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFD97706"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Kunci</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Nilai</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>NAMA_INSTANSI</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Politeknik Kesehatan Kemenkes Palembang</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>Nama instansi pada notifikasi</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>EMAIL_NOTIF</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>lukman@poltekkespalembang.ac.id, kerjasama@poltekkespalembang.ac.id, okta@poltekkespalembang.ac.id</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Penerima notifikasi reminder (pisahkan dengan koma)</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>kerjasama@poltekkespalembang.ac.id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Email tim INTERNAL penerima rekap (pisahkan koma)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>BASE_URL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>https://simkerma.vercel.app</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Domain aplikasi (ubah saat pindah domain instansi)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMINDER_HARI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>90,60,30,7,0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ambang reminder H- dalam hari, pisahkan koma. 0 = hari berakhir</t>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>REMINDER_CADENCE</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>90:30,60:14,30:7,7:1</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Jadwal ingat "sisa:interval" hari. Makin dekat makin sering. Mis. 90:30,60:14,30:7,7:1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>GRACE_HABIS_HARI</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Setelah berakhir, tetap ingatkan harian sampai N hari, lalu berhenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>EMAIL_AKTIF</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Aktifkan notifikasi Email (TRUE/FALSE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WA_AKTIF</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Aktifkan email rekap INTERNAL (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>WA_NOMOR_AKTIF</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Aktifkan notifikasi WhatsApp (TRUE/FALSE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Aktifkan WA rekap ke NOMOR perorangan tim (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>WA_TARGET</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nomor WhatsApp tujuan (mis. 62812xxxx), pisahkan koma</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Nomor WA tim internal (mis. 62812xxxx), pisahkan koma</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>WA_GRUP_AKTIF</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Aktifkan WA rekap ke GRUP (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>WA_GRUP_ID</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>ID grup WhatsApp (Fonnte) untuk rekap internal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>LAMPIRKAN_FILE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Lampirkan file MoU/PKS pada email reminder (TRUE/FALSE)</t>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Lampirkan file MoU/PKS pada email (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>EMAIL_EKSTERNAL_AKTIF</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Aktifkan EMAIL ke PIC mitra — hanya kerja sama miliknya (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>WA_EKSTERNAL_AKTIF</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>HATI-HATI: WA ke PIC mitra. Bila banyak, nomor Fonnte bisa diblokir (TRUE/FALSE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>WA_EKSTERNAL_MAKS_PER_HARI</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Batas jumlah WA eksternal per hari (anti-blokir). Mis. 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>WA_EKSTERNAL_JEDA_DETIK</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Jeda antar kirim WA eksternal dalam detik (anti-burst). Mis. 8</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mitra'!$A$1:$I$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kerjasama'!$A$1:$X$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dataset'!$A$1:$B$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pengaturan'!$A$1:$C$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pengaturan'!$A$1:$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -149,6 +149,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9333,7 +9339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9359,12 +9365,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>NAMA_INSTANSI</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Politeknik Kesehatan Kemenkes Palembang</t>
         </is>
@@ -9376,12 +9382,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>EMAIL_NOTIF</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -9393,12 +9399,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>BASE_URL</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>https://simkerma.vercel.app</t>
         </is>
@@ -9410,12 +9416,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>REMINDER_CADENCE</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>90:30,60:14,30:7,7:1</t>
         </is>
@@ -9427,12 +9433,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>GRACE_HABIS_HARI</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="14" t="n">
         <v>14</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -9442,12 +9448,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>EMAIL_AKTIF</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -9459,12 +9465,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>WA_NOMOR_AKTIF</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9476,12 +9482,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WA_TARGET</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Nomor WA tim internal (mis. 62812xxxx), pisahkan koma</t>
@@ -9489,12 +9495,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WA_GRUP_AKTIF</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9506,12 +9512,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>WA_GRUP_ID</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
           <t>ID grup WhatsApp (Fonnte) untuk rekap internal</t>
@@ -9519,12 +9525,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>LAMPIRKAN_FILE</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -9536,12 +9542,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>EMAIL_EKSTERNAL_AKTIF</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9553,12 +9559,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_AKTIF</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9570,12 +9576,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_MAKS_PER_HARI</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9585,12 +9591,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_JEDA_DETIK</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -9599,8 +9605,25 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>SURVEY_AKTIF</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Tampilkan overlay survei tahunan (mulai November). FALSE = matikan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C16"/>
+  <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Template_Spreadsheet_MonitoringKerjasama.xlsx
+++ b/Template_Spreadsheet_MonitoringKerjasama.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mitra'!$A$1:$I$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kerjasama'!$A$1:$X$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kerjasama'!$A$1:$Y$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dataset'!$A$1:$B$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pengaturan'!$A$1:$C$17</definedName>
   </definedNames>
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -126,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -150,6 +151,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1972,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:Y96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1995,10 +2003,11 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2104,20 +2113,25 @@
       </c>
       <c r="U1" s="6" t="inlineStr">
         <is>
+          <t>Tindak Lanjut</t>
+        </is>
+      </c>
+      <c r="V1" s="6" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Sisa Hari</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Diinput Oleh</t>
         </is>
       </c>
-      <c r="X1" s="6" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>Reminder Terakhir</t>
         </is>
@@ -2199,15 +2213,15 @@
           <t>Riset bersama; konfirmasi lanjut</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="V2" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>19</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2284,15 +2298,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="V3" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>29</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2379,15 +2393,15 @@
           <t>Segera jatuh tempo, siapkan perpanjangan</t>
         </is>
       </c>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="V4" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>44</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2464,15 +2478,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>59</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2554,15 +2568,15 @@
           <t>Sudah diperpanjang</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>-470</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2644,15 +2658,15 @@
           <t>Habis baru-baru ini</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>-41</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2739,15 +2753,15 @@
           <t>Menunggu konfirmasi mitra untuk perpanjangan</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>-31</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2829,15 +2843,15 @@
           <t>Berakhir hari ini — segera tindak lanjut</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-1</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -2919,15 +2933,15 @@
           <t>Kontrak penyediaan tenaga; nilai besar</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="V10" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>164</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3004,15 +3018,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U11" s="9" t="inlineStr">
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>164</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3094,15 +3108,15 @@
           <t>Tidak diperpanjang — klinik pindah kepemilikan</t>
         </is>
       </c>
-      <c r="U12" s="9" t="inlineStr">
+      <c r="V12" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>229</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3189,15 +3203,15 @@
           <t>Addendum penambahan ruang lingkup</t>
         </is>
       </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="V13" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>344</v>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3274,15 +3288,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U14" s="9" t="inlineStr">
+      <c r="V14" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>349</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3359,15 +3373,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr">
+      <c r="V15" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>429</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3444,15 +3458,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U16" s="9" t="inlineStr">
+      <c r="V16" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>630</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3529,15 +3543,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U17" s="9" t="inlineStr">
+      <c r="V17" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>710</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3614,15 +3628,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U18" s="9" t="inlineStr">
+      <c r="V18" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>770</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3699,15 +3713,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U19" s="9" t="inlineStr">
+      <c r="V19" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>800</v>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3784,15 +3798,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U20" s="9" t="inlineStr">
+      <c r="V20" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>815</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3869,15 +3883,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="V21" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>865</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -3954,15 +3968,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U22" s="9" t="inlineStr">
+      <c r="V22" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>880</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4044,15 +4058,15 @@
           <t>K-0001</t>
         </is>
       </c>
-      <c r="U23" s="9" t="inlineStr">
+      <c r="V23" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>895</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4134,15 +4148,15 @@
           <t>HK.03.01/1.3/395</t>
         </is>
       </c>
-      <c r="U24" s="9" t="inlineStr">
+      <c r="V24" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>945</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4219,15 +4233,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U25" s="9" t="inlineStr">
+      <c r="V25" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>960</v>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4309,15 +4323,15 @@
           <t>K-0010</t>
         </is>
       </c>
-      <c r="U26" s="9" t="inlineStr">
+      <c r="V26" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>975</v>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4399,15 +4413,15 @@
           <t>K-0007</t>
         </is>
       </c>
-      <c r="U27" s="9" t="inlineStr">
+      <c r="V27" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>995</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4484,15 +4498,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U28" s="9" t="inlineStr">
+      <c r="V28" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>1015</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4569,15 +4583,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U29" s="9" t="inlineStr">
+      <c r="V29" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>1035</v>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4654,15 +4668,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U30" s="9" t="inlineStr">
+      <c r="V30" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>1100</v>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4739,15 +4753,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U31" s="9" t="inlineStr">
+      <c r="V31" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>1125</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4824,15 +4838,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U32" s="9" t="inlineStr">
+      <c r="V32" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>1225</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4909,15 +4923,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U33" s="9" t="inlineStr">
+      <c r="V33" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>1315</v>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -4994,15 +5008,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U34" s="9" t="inlineStr">
+      <c r="V34" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>1345</v>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5079,15 +5093,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U35" s="9" t="inlineStr">
+      <c r="V35" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>1395</v>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5164,15 +5178,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U36" s="9" t="inlineStr">
+      <c r="V36" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>1425</v>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5249,15 +5263,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U37" s="9" t="inlineStr">
+      <c r="V37" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>1475</v>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5334,15 +5348,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U38" s="9" t="inlineStr">
+      <c r="V38" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>1495</v>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5419,15 +5433,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U39" s="9" t="inlineStr">
+      <c r="V39" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>1525</v>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5504,15 +5518,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U40" s="9" t="inlineStr">
+      <c r="V40" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>1575</v>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5589,15 +5603,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U41" s="9" t="inlineStr">
+      <c r="V41" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>1595</v>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5674,15 +5688,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U42" s="9" t="inlineStr">
+      <c r="V42" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>1735</v>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5759,15 +5773,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U43" s="9" t="inlineStr">
+      <c r="V43" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>1794</v>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5844,15 +5858,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U44" s="9" t="inlineStr">
+      <c r="V44" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>2425</v>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -5929,15 +5943,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U45" s="9" t="inlineStr">
+      <c r="V45" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>2725</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6014,15 +6028,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U46" s="9" t="inlineStr">
+      <c r="V46" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>225</v>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6099,15 +6113,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="V47" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>-429</v>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6184,15 +6198,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U48" s="7" t="inlineStr">
+      <c r="V48" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>11</v>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6274,15 +6288,15 @@
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U49" s="9" t="inlineStr">
+      <c r="V49" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>743</v>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6364,15 +6378,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U50" s="9" t="inlineStr">
+      <c r="V50" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>1049</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6454,15 +6468,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="V51" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>-227</v>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6539,15 +6553,15 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="V52" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>-420</v>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6624,15 +6638,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U53" s="7" t="inlineStr">
+      <c r="V53" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>43</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6714,15 +6728,15 @@
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>-98</v>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6799,15 +6813,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U55" s="7" t="inlineStr">
+      <c r="V55" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>35</v>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6889,15 +6903,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>-154</v>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -6974,15 +6988,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U57" s="7" t="inlineStr">
+      <c r="V57" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>23</v>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7064,15 +7078,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U58" s="7" t="inlineStr">
+      <c r="V58" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>27</v>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7154,15 +7168,15 @@
           <t>Proses perpanjangan</t>
         </is>
       </c>
-      <c r="U59" s="9" t="inlineStr">
+      <c r="V59" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>1185</v>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7239,15 +7253,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U60" s="7" t="inlineStr">
+      <c r="V60" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>65</v>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7324,15 +7338,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U61" s="7" t="inlineStr">
+      <c r="V61" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>18</v>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7414,15 +7428,15 @@
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U62" s="9" t="inlineStr">
+      <c r="V62" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>182</v>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7499,15 +7513,15 @@
           <t>Perpanjangan</t>
         </is>
       </c>
-      <c r="U63" s="9" t="inlineStr">
+      <c r="V63" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V63" t="n">
+      <c r="W63" t="n">
         <v>875</v>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7584,15 +7598,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
+      <c r="V64" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V64" t="n">
+      <c r="W64" t="n">
         <v>-55</v>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7674,15 +7688,15 @@
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U65" s="7" t="inlineStr">
+      <c r="V65" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V65" t="n">
+      <c r="W65" t="n">
         <v>6</v>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7764,15 +7778,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U66" s="9" t="inlineStr">
+      <c r="V66" s="9" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="V66" t="n">
+      <c r="W66" t="n">
         <v>664</v>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7849,15 +7863,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U67" s="7" t="inlineStr">
+      <c r="V67" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V67" t="n">
+      <c r="W67" t="n">
         <v>28</v>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -7939,15 +7953,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U68" s="8" t="inlineStr">
+      <c r="V68" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V68" t="n">
+      <c r="W68" t="n">
         <v>-26</v>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8024,15 +8038,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U69" s="8" t="inlineStr">
+      <c r="V69" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V69" t="n">
+      <c r="W69" t="n">
         <v>-517</v>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8114,15 +8128,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U70" s="7" t="inlineStr">
+      <c r="V70" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V70" t="n">
+      <c r="W70" t="n">
         <v>47</v>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8204,15 +8218,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U71" s="8" t="inlineStr">
+      <c r="V71" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V71" t="n">
+      <c r="W71" t="n">
         <v>-73</v>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8289,15 +8303,15 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U72" s="8" t="inlineStr">
+      <c r="V72" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V72" t="n">
+      <c r="W72" t="n">
         <v>-214</v>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8379,15 +8393,15 @@
           <t>Perlu addendum</t>
         </is>
       </c>
-      <c r="U73" s="7" t="inlineStr">
+      <c r="V73" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V73" t="n">
+      <c r="W73" t="n">
         <v>23</v>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8469,15 +8483,15 @@
           <t>Proses perpanjangan</t>
         </is>
       </c>
-      <c r="U74" s="7" t="inlineStr">
+      <c r="V74" s="7" t="inlineStr">
         <is>
           <t>Segera Berakhir</t>
         </is>
       </c>
-      <c r="V74" t="n">
+      <c r="W74" t="n">
         <v>74</v>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8559,15 +8573,15 @@
           <t>Menunggu konfirmasi mitra</t>
         </is>
       </c>
-      <c r="U75" s="8" t="inlineStr">
+      <c r="V75" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>-26</v>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -8644,22 +8658,1686 @@
           <t>Baru</t>
         </is>
       </c>
-      <c r="U76" s="8" t="inlineStr">
+      <c r="V76" s="8" t="inlineStr">
         <is>
           <t>Habis</t>
         </is>
       </c>
-      <c r="V76" t="n">
+      <c r="W76" t="n">
         <v>-43</v>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>K-UJI-001</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n">
+        <v>46224.99988977212</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>UJI COBA 01 — H-88</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>UJI/001</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="15" t="n">
+        <v>45943</v>
+      </c>
+      <c r="O77" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>88</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>K-UJI-002</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n">
+        <v>46224.99988977237</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>UJI COBA 02 — H-75</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UJI/002</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="15" t="n">
+        <v>45930</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>75</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>K-UJI-003</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="n">
+        <v>46224.99988977248</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>UJI COBA 03 — H-66</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UJI/003</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="15" t="n">
+        <v>45921</v>
+      </c>
+      <c r="O79" s="15" t="n">
+        <v>46286</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>66</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>K-UJI-004</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n">
+        <v>46224.99988977255</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>UJI COBA 04 — H-58</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>UJI/004</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="15" t="n">
+        <v>45913</v>
+      </c>
+      <c r="O80" s="15" t="n">
+        <v>46278</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W80" t="n">
+        <v>58</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>K-UJI-005</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n">
+        <v>46224.99988977262</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>UJI COBA 05 — H-45</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>UJI/005</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="15" t="n">
+        <v>45900</v>
+      </c>
+      <c r="O81" s="15" t="n">
+        <v>46265</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Tidak Diperpanjang</t>
+        </is>
+      </c>
+      <c r="V81" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W81" t="n">
+        <v>45</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>K-UJI-006</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n">
+        <v>46224.99988977268</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>UJI COBA 06 — H-33</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UJI/006</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="15" t="n">
+        <v>45888</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>46253</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W82" t="n">
+        <v>33</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>K-UJI-007</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="n">
+        <v>46224.99988977274</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UJI COBA 07 — H-28</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>UJI/007</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="15" t="n">
+        <v>45883</v>
+      </c>
+      <c r="O83" s="15" t="n">
+        <v>46248</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W83" t="n">
+        <v>28</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>K-UJI-008</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="n">
+        <v>46224.99988977281</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UJI COBA 08 — H-20</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UJI/008</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="15" t="n">
+        <v>45875</v>
+      </c>
+      <c r="O84" s="15" t="n">
+        <v>46240</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W84" t="n">
+        <v>20</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>K-UJI-009</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="n">
+        <v>46224.99988977287</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UJI COBA 09 — H-12</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>UJI/009</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="15" t="n">
+        <v>45867</v>
+      </c>
+      <c r="O85" s="15" t="n">
+        <v>46232</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W85" t="n">
+        <v>12</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>K-UJI-010</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="n">
+        <v>46224.99988977293</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UJI COBA 10 — H-9</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UJI/010</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="15" t="n">
+        <v>45864</v>
+      </c>
+      <c r="O86" s="15" t="n">
+        <v>46229</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W86" t="n">
+        <v>9</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>K-UJI-011</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="n">
+        <v>46224.999889773</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>UJI COBA 11 — H-7</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>UJI/011</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="15" t="n">
+        <v>45862</v>
+      </c>
+      <c r="O87" s="15" t="n">
+        <v>46227</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W87" t="n">
+        <v>7</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>K-UJI-012</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n">
+        <v>46224.99988977305</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>UJI COBA 12 — H-5</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>UJI/012</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="15" t="n">
+        <v>45860</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>46225</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W88" t="n">
+        <v>5</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>K-UJI-013</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="n">
+        <v>46224.99988977313</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>UJI COBA 13 — H-3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>UJI/013</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" s="15" t="n">
+        <v>45858</v>
+      </c>
+      <c r="O89" s="15" t="n">
+        <v>46223</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W89" t="n">
+        <v>3</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>K-UJI-014</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>46224.99988977319</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>UJI COBA 14 — H-1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>UJI/014</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" s="15" t="n">
+        <v>45856</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>46221</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W90" t="n">
+        <v>1</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>K-UJI-015</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n">
+        <v>46224.99988977325</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>UJI COBA 15 — HARI-H</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UJI/015</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" s="15" t="n">
+        <v>45855</v>
+      </c>
+      <c r="O91" s="15" t="n">
+        <v>46220</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" s="7" t="inlineStr">
+        <is>
+          <t>Segera Berakhir</t>
+        </is>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>K-UJI-016</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="n">
+        <v>46224.99988977333</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>UJI COBA 16 — habis 1h</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>UJI/016</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" s="15" t="n">
+        <v>45854</v>
+      </c>
+      <c r="O92" s="15" t="n">
+        <v>46219</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" s="8" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="W92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>K-UJI-017</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="n">
+        <v>46224.99988977339</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>UJI COBA 17 — habis 3h</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>UJI/017</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="15" t="n">
+        <v>45852</v>
+      </c>
+      <c r="O93" s="15" t="n">
+        <v>46217</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" s="8" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="W93" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>K-UJI-018</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>46224.99988977346</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>UJI COBA 18 — habis 7h</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>UJI/018</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" s="15" t="n">
+        <v>45848</v>
+      </c>
+      <c r="O94" s="15" t="n">
+        <v>46213</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" s="8" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="W94" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>K-UJI-019</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="n">
+        <v>46224.99988977353</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>UJI COBA 19 — habis 12h</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>UJI/019</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" s="15" t="n">
+        <v>45843</v>
+      </c>
+      <c r="O95" s="15" t="n">
+        <v>46208</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" s="8" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="W95" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>K-UJI-020</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="n">
+        <v>46224.9998897736</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>UJI COBA 20 — habis 20h</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Uji Coba</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>UJI/020</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Perjanjian Kerja sama (PKS)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Pendidikan</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Prodi DIII Gizi</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" s="15" t="n">
+        <v>45835</v>
+      </c>
+      <c r="O96" s="15" t="n">
+        <v>46200</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Baru</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Data uji notif — boleh dihapus</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" s="8" t="inlineStr">
+        <is>
+          <t>Habis</t>
+        </is>
+      </c>
+      <c r="W96" t="n">
+        <v>-20</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>uji@contoh.id</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X76"/>
+  <autoFilter ref="A1:Y96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9365,12 +11043,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>NAMA_INSTANSI</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Politeknik Kesehatan Kemenkes Palembang</t>
         </is>
@@ -9382,12 +11060,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>EMAIL_NOTIF</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>kerjasama@poltekkespalembang.ac.id</t>
         </is>
@@ -9399,12 +11077,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>BASE_URL</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>https://simkerma.vercel.app</t>
         </is>
@@ -9416,12 +11094,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>REMINDER_CADENCE</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>90:30,60:14,30:7,7:1</t>
         </is>
@@ -9433,12 +11111,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>GRACE_HABIS_HARI</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>14</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -9448,12 +11126,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EMAIL_AKTIF</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -9465,12 +11143,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>WA_NOMOR_AKTIF</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9482,12 +11160,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>WA_TARGET</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
+      <c r="B9" s="17" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Nomor WA tim internal (mis. 62812xxxx), pisahkan koma</t>
@@ -9495,12 +11173,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>WA_GRUP_AKTIF</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9512,12 +11190,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>WA_GRUP_ID</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr"/>
       <c r="C11" s="12" t="inlineStr">
         <is>
           <t>ID grup WhatsApp (Fonnte) untuk rekap internal</t>
@@ -9525,12 +11203,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>LAMPIRKAN_FILE</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -9542,12 +11220,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>EMAIL_EKSTERNAL_AKTIF</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9559,12 +11237,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_AKTIF</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
@@ -9576,12 +11254,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_MAKS_PER_HARI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="17" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -9591,12 +11269,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>WA_EKSTERNAL_JEDA_DETIK</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="17" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -9606,12 +11284,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>SURVEY_AKTIF</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
